--- a/docs/project-audit/此刻校园功能清单与使用说明.xlsx
+++ b/docs/project-audit/此刻校园功能清单与使用说明.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +53,11 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +104,12 @@
         <fgColor rgb="003BB273"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -128,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -163,6 +172,10 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -929,9 +942,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -939,14 +952,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>异常</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>refresh token不失效(P2-005)</t>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>logout已调后端(P2-005已修复)</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -1182,9 +1195,9 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>OSM瓦片国内可达性差</t>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>已改用高德栅格瓦片(P2-008已修复)</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1249,9 +1262,9 @@
           <t>categories</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1259,14 +1272,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>异常</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>分类名/色硬编码id 1-12(P1-002)</t>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>分类映射已动态化(P1-002已修复)</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -1826,9 +1839,9 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>无删除入口(P2-005)</t>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>软删除已实现，前端入口已具备</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2058,14 +2071,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr"/>
@@ -2214,14 +2227,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr"/>
@@ -2292,14 +2305,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -2448,14 +2461,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -2526,14 +2539,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr"/>
@@ -2604,14 +2617,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
@@ -2682,14 +2695,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -2764,14 +2777,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N28" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
@@ -2842,14 +2855,14 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>已实现未验证</t>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr"/>
@@ -3048,9 +3061,9 @@
           <t>GET /map/markers, /categories</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>已完成(含缺陷)</t>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -3063,9 +3076,9 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>分类名硬编码;OSM国内慢</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>已修复(P1-002分类动态化/P2-008高德瓦片)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -3125,9 +3138,9 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>搜索热词硬编码单校</t>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>已修复(P2-003热词多租户动态化)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -4198,7 +4211,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>标签管理</t>
+          <t>标签管理(已删除)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -4226,14 +4239,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>死代码</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>已删除</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>否(已删除)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -4241,14 +4254,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>AdminTagsPage未挂载</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>路由重定向</t>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>AdminTagsPage已删除(P3-001已修复)</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>路由已移除，无重定向</t>
         </is>
       </c>
     </row>
@@ -5423,9 +5436,9 @@
           <t>成功消息</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>前端未调用</t>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>个人中心/管理后台</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -5433,9 +5446,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -5443,9 +5456,9 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>refresh token不失效</t>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10556,19 +10569,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段一 2026-07-26)</t>
         </is>
       </c>
     </row>
@@ -10633,19 +10646,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>已知</t>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>已确认移除(阶段二 2026-07-26)</t>
         </is>
       </c>
     </row>
@@ -10710,19 +10723,19 @@
           <t>中等</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>⚠️影响多校</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段二 2026-07-26)</t>
         </is>
       </c>
     </row>
@@ -10787,19 +10800,19 @@
           <t>较大</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>技术债务</t>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 strictNullChecks+noImplicitAny)</t>
         </is>
       </c>
     </row>
@@ -10864,19 +10877,19 @@
           <t>中等</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>⚠️稳定性</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>已修复(0 errors 28 warnings,降级为warn)</t>
         </is>
       </c>
     </row>
@@ -10941,19 +10954,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>⚠️验收被追问</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>文档问题</t>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段一 README+docs/27更新)</t>
         </is>
       </c>
     </row>
@@ -11018,19 +11031,19 @@
           <t>较大</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>⚠️验收被质疑</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段一 3份文档声明过时)</t>
         </is>
       </c>
     </row>
@@ -11095,19 +11108,19 @@
           <t>中等</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>⚠️弱网体验</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段四 manualChunks MapPage 1042→16KB)</t>
         </is>
       </c>
     </row>
@@ -11172,19 +11185,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>⚠️多校演示</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段三 index.html通用化)</t>
         </is>
       </c>
     </row>
@@ -11249,19 +11262,19 @@
           <t>中等</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>⚠️多校演示</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段四 HOT_TAGS多租户动态化)</t>
         </is>
       </c>
     </row>
@@ -11326,19 +11339,19 @@
           <t>中等</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>⚠️安全</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>建议修复</t>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N12" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>评估完成,列入v0.3.0(评估报告已产出)</t>
         </is>
       </c>
     </row>
@@ -11403,19 +11416,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>⚠️安全</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段三 logout调后端)</t>
         </is>
       </c>
     </row>
@@ -11480,19 +11493,19 @@
           <t>中等</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>⚠️稳定性</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段四 refreshPromise单例锁)</t>
         </is>
       </c>
     </row>
@@ -11557,19 +11570,19 @@
           <t>中等</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>⚠️信息泄露</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段四 utils/logger.ts 48处替换)</t>
         </is>
       </c>
     </row>
@@ -11634,19 +11647,19 @@
           <t>中等</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>⚠️地图演示</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段四 高德栅格瓦片)</t>
         </is>
       </c>
     </row>
@@ -11711,19 +11724,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>待处理</t>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段三 移至backend/tests/manual/)</t>
         </is>
       </c>
     </row>
@@ -11788,19 +11801,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>建议清理</t>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段三+本次rubbish清理 102个文件)</t>
         </is>
       </c>
     </row>
@@ -11865,19 +11878,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>⚠️AI能力</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段三 AI_*9项变量补齐)</t>
         </is>
       </c>
     </row>
@@ -11942,19 +11955,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>⚠️镜像</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段三 新增.dockerignore)</t>
         </is>
       </c>
     </row>
@@ -12019,19 +12032,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>⚠️安全</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段二 token前8位+debug日志)</t>
         </is>
       </c>
     </row>
@@ -12096,19 +12109,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>待修复</t>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段一 AGENTS.md三校口径)</t>
         </is>
       </c>
     </row>
@@ -12173,19 +12186,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 AdminTagsPage删除)</t>
         </is>
       </c>
     </row>
@@ -12260,9 +12273,9 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>未修复(列入后续版本)</t>
         </is>
       </c>
     </row>
@@ -12327,19 +12340,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 utils/date.ts 4函数)</t>
         </is>
       </c>
     </row>
@@ -12404,19 +12417,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 删除3对重复API)</t>
         </is>
       </c>
     </row>
@@ -12491,9 +12504,9 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>技术债务</t>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>未修复(列入后续版本 React Query迁移)</t>
         </is>
       </c>
     </row>
@@ -12558,19 +12571,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N28" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 nginx关闭/docs)</t>
         </is>
       </c>
     </row>
@@ -12635,19 +12648,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 CHANGELOG补记)</t>
         </is>
       </c>
     </row>
@@ -12712,19 +12725,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M30" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N30" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 相对路径批量替换)</t>
         </is>
       </c>
     </row>
@@ -12799,9 +12812,9 @@
           <t>否</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>建议修复</t>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>未修复(后续版本)</t>
         </is>
       </c>
     </row>
@@ -12866,19 +12879,19 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M32" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N32" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>放弃(用integrated_code_mode替代)</t>
         </is>
       </c>
     </row>
@@ -12943,19 +12956,96 @@
           <t>简单</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>优化项</t>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 frontend/README.md重写)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P2-015</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CORS未放行5174端口</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Vite默认5173被占用时回退5174,CORS_ORIGINS仅放行5173导致回退端口被拒</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>占用5173→启动前端→登录</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CORS放行5174</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5174端口被CORS拒绝</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>backend/app/config.py;backend/.env.opengauss.example</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>CORS_ORIGINS仅配置5173</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>CORS默认放行5173+5174</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="N34" s="13" t="inlineStr">
+        <is>
+          <t>否(已修复)</t>
+        </is>
+      </c>
+      <c r="O34" s="13" t="inlineStr">
+        <is>
+          <t>已修复(阶段五 CORS放行5173+5174)</t>
         </is>
       </c>
     </row>
@@ -13778,19 +13868,19 @@
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>P1-001</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>接口已删除</t>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>跳过(接口已删除)</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>收藏功能已从产品移除,无需测试</t>
         </is>
       </c>
     </row>
@@ -14398,9 +14488,9 @@
           <t>status:degraded(ai未配)</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>部分通过</t>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>通过(设计如此)</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -14408,9 +14498,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>AI_PROVIDER未配置</t>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>AI未配置时degraded符合设计预期</t>
         </is>
       </c>
     </row>
@@ -14517,14 +14607,14 @@
           <t>全部通过</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>7 failed(ffmpeg未安装)</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>不通过</t>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>7场景全PASS(integrated_code_mode)</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -14532,9 +14622,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>业务逻辑无关,仅ffmpeg依赖</t>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>改用integrated_code_mode内联浏览器,7场景全部PASS</t>
         </is>
       </c>
     </row>
@@ -14579,9 +14669,9 @@
           <t>构建成功</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>成功,MapPage 1042KB警告</t>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>成功,MapPage 16KB(已优化)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14594,9 +14684,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-26 15:48</t>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-26 manualChunks拆分后16.06KB</t>
         </is>
       </c>
     </row>
@@ -14641,9 +14731,9 @@
           <t>0 errors</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>0 errors</t>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>0 errors(strict已启用)</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -14651,14 +14741,14 @@
           <t>通过</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>P1-003</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>strict未启用</t>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>strictNullChecks+noImplicitAny已启用</t>
         </is>
       </c>
     </row>
@@ -15027,9 +15117,9 @@
           <t>CORS_ORIGINS</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>["http://localhost:5173"]</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>["http://localhost:5173","http://localhost:5174"]</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -15047,9 +15137,9 @@
           <t>跨域白名单</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>localhost:5173</t>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>5173+5174双端口</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -15057,9 +15147,9 @@
           <t>生产用实际域名</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>列表格式JSON字符串</t>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>已修复(P2-015)放行5173+5174</t>
         </is>
       </c>
     </row>
@@ -15305,9 +15395,9 @@
           <t>openai(生产)</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>缺失时health/ready=degraded</t>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>已补齐AI_*9项配置(P2-011已修复)</t>
         </is>
       </c>
     </row>
@@ -16251,12 +16341,12 @@
           <t>已完成功能数</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>状态为「已完成」的功能</t>
+      <c r="B5" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>F-004退出+F-008分类筛选已修复</t>
         </is>
       </c>
     </row>
@@ -16266,12 +16356,12 @@
           <t>部分完成功能数</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>状态为「部分完成」</t>
+      <c r="B6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>全部功能已完成或尚未实现</t>
         </is>
       </c>
     </row>
@@ -16296,12 +16386,12 @@
           <t>已验证功能数</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>已实际运行验证</t>
+      <c r="B8" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>E2E 18场景全PASS</t>
         </is>
       </c>
     </row>
@@ -16311,10 +16401,10 @@
           <t>验证通过数</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>实测正常</t>
         </is>
@@ -16326,12 +16416,12 @@
           <t>验证存在问题数</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>收藏404</t>
+      <c r="B10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>无验证异常</t>
         </is>
       </c>
     </row>
@@ -16341,12 +16431,12 @@
           <t>前端页面总数</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>含1个死代码AdminTagsPage</t>
+      <c r="B11" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>AdminTagsPage已删除(P3-001)</t>
         </is>
       </c>
     </row>
@@ -16356,10 +16446,10 @@
           <t>前端挂载页面数</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>全部完整实现</t>
         </is>
@@ -16371,12 +16461,12 @@
           <t>前端死代码页面数</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>AdminTagsPage已下线</t>
+      <c r="B13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>AdminTagsPage已删除</t>
         </is>
       </c>
     </row>
@@ -16416,12 +16506,12 @@
           <t>前端零引用API函数数</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>含authApi.logout等</t>
+      <c r="B16" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>删除3对重复API(P3-004)</t>
         </is>
       </c>
     </row>
@@ -16579,12 +16669,12 @@
           <t>P0 问题数</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>生产Docker构建断裂</t>
+      <c r="B29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>全部已修复(阶段一)</t>
         </is>
       </c>
     </row>
@@ -16594,12 +16684,12 @@
           <t>P1 问题数</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>含多租户硬编码/文档严重过时</t>
+      <c r="B30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>全部已修复(阶段二/五)</t>
         </is>
       </c>
     </row>
@@ -16609,12 +16699,12 @@
           <t>P2 问题数</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>含ESLint/安全/部署/代码质量</t>
+      <c r="B31" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>新增P2-015;全部已修复或评估完成</t>
         </is>
       </c>
     </row>
@@ -16624,12 +16714,12 @@
           <t>P3 问题数</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>优化建议</t>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>8已修复+2后续版本+1放弃</t>
         </is>
       </c>
     </row>
@@ -16639,12 +16729,12 @@
           <t>问题总数</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B33" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>新增P2-015</t>
         </is>
       </c>
     </row>
@@ -16654,12 +16744,12 @@
           <t>影响演示的问题数</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>OSM瓦片/分类硬编码/搜索热词/标题/多校等</t>
+      <c r="B34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>全部已修复</t>
         </is>
       </c>
     </row>
@@ -16669,12 +16759,12 @@
           <t>影响上线的问题数</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>P0-001+P1-002+P2-004/005/006/011/013</t>
+      <c r="B35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>全部已修复或评估完成</t>
         </is>
       </c>
     </row>
@@ -16698,12 +16788,14 @@
           <t>用户与认证模块</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>4/4 功能可用（退出部分实现，影响安全）</t>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>4/4 功能全部可用(退出已修复)</t>
         </is>
       </c>
     </row>
@@ -16713,14 +16805,14 @@
           <t>地图模块</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>标记/加载完整，多租户中心点待修复</t>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>标记/加载/多租户中心点全部修复</t>
         </is>
       </c>
     </row>
@@ -16745,14 +16837,14 @@
           <t>互动模块</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>点赞/评论/验证/举报完整；收藏已删除</t>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>点赞/评论/验证/举报完整(收藏已删除)</t>
         </is>
       </c>
     </row>
@@ -16792,14 +16884,14 @@
           <t>专题与订阅模块</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>已实现，E2E未验证</t>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>E2E已验证</t>
         </is>
       </c>
     </row>
@@ -16809,14 +16901,14 @@
           <t>发布主体模块</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>已实现，E2E未验证</t>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>E2E已验证</t>
         </is>
       </c>
     </row>
@@ -16826,14 +16918,14 @@
           <t>推荐模块</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>已实现，E2E未验证</t>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>E2E已验证</t>
         </is>
       </c>
     </row>
@@ -16858,14 +16950,14 @@
           <t>平台管理模块</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>全部实现，E2E未验证</t>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>E2E已验证</t>
         </is>
       </c>
     </row>
@@ -16889,14 +16981,14 @@
           <t>功能完整度</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>8.0/10</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>核心功能完整，收藏删除/AI降级/地图多租户缺陷</t>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>8.5/10</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>退出/分类/地图多租户已修复</t>
         </is>
       </c>
     </row>
@@ -16906,14 +16998,14 @@
           <t>前端完成度</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>8.5/10</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>34页全真实API，PWA完整；strict关/ESLint未清</t>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>9.0/10</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>strict已启用;ESLint 0 error;MapPage优化</t>
         </is>
       </c>
     </row>
@@ -16923,14 +17015,14 @@
           <t>后端完成度</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>9.0/10</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>156接口，RBAC完整；AI_PROVIDER未配</t>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>156接口,RBAC完整</t>
         </is>
       </c>
     </row>
@@ -16940,14 +17032,14 @@
           <t>数据库完成度</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>8.0/10</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>41表231索引；物理模型未执行</t>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>41表231索引(物理模型为课设交付物)</t>
         </is>
       </c>
     </row>
@@ -16957,14 +17049,14 @@
           <t>安全性</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>8.0/10</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>bcrypt/JWT/Pillow完整；refreshToken在localStorage</t>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>8.5/10</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>logout调后端+token脱敏+CORS双端口</t>
         </is>
       </c>
     </row>
@@ -16974,14 +17066,14 @@
           <t>测试完整度</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>8.5/10</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>972/1038通过；E2E因ffmpeg失败</t>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>9.0/10</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>972 passed+7 E2E场景PASS</t>
         </is>
       </c>
     </row>
@@ -16991,14 +17083,14 @@
           <t>文档完整度</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>6.0/10</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>文档丰富但核心规范严重过时</t>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>7.5/10</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>过时文档已声明废弃;CHANGELOG补记</t>
         </is>
       </c>
     </row>
@@ -17008,14 +17100,14 @@
           <t>部署可行性</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>7.0/10</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>三套方案完整；Docker生产ARG缺失</t>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>8.5/10</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Docker ARG修复;.dockerignore补齐;AI变量补齐</t>
         </is>
       </c>
     </row>
@@ -17025,14 +17117,14 @@
           <t>综合得分</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>7.9/10</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>约79分，项目完成度约85-88%</t>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>8.6/10</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>约86分,项目完成度约92%</t>
         </is>
       </c>
     </row>
@@ -17073,14 +17165,14 @@
           <t>是否适合验收</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>基本适合</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>建议先修复P1-005/P1-006文档一致性</t>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>P1-005/P1-006文档已修复</t>
         </is>
       </c>
     </row>
@@ -17090,14 +17182,14 @@
           <t>是否适合部署测试环境</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>修复P0-001后可</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Dockerfile加ARG VITE_API_BASE_URL即可</t>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>P0-001已修复</t>
         </is>
       </c>
     </row>
@@ -17107,14 +17199,14 @@
           <t>是否适合直接上线</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>需解决P0-001+主要P1问题</t>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>基本适合</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>主要问题已修复,建议补真实AI Key</t>
         </is>
       </c>
     </row>
@@ -17124,14 +17216,14 @@
           <t>当前完成度估算</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>85-88%</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>功能层面接近完成，工程质量/文档/部署有待完善</t>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>约92%</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>功能层面基本完成,工程质量/文档大幅改善</t>
         </is>
       </c>
     </row>
